--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2e0f891b3d154055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rd2ef4a53c9ed4c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R57b8e20616de44f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R1e74dc397d1a4c8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0ffe033fe8194e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rcc475f5943b5496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R22690588016d4540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R3e51d3e0169a45e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4a5ddf8af1c042b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R271c1628443a4af1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,7 +38,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2C5E86"/>
+        <x:fgColor rgb="FF315D72"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -46,14 +46,14 @@
     <x:border/>
     <x:border>
       <x:bottom style="thin">
-        <x:color rgb="FFD7E2EA"/>
+        <x:color rgb="FFD6E0E5"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -74,9 +74,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -280,23 +277,23 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="62" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="86" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="66" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>交付物名称</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
-        <x:v>固定路径/命名规则</x:v>
-      </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="B1" s="8" t="str">
+        <x:v>固定路径或命名规则</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
         <x:v>用途</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>判定方式</x:v>
       </x:c>
     </x:row>
@@ -322,7 +319,7 @@
         <x:v>output/kustomize/overlays</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>保存canary、promote和rollback三个阶段差异</x:v>
+        <x:v>保存canary、promote和rollback差异</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>逐层构建并核对目标字段</x:v>
@@ -330,142 +327,86 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>执行入口</x:v>
+        <x:v>四阶段清单</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>output/run_release_review.rb</x:v>
+        <x:v>output/results/rendered_base.yaml、rendered_canary.yaml、rendered_promote.yaml、rendered_rollback.yaml</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>从输入材料生成结果</x:v>
+        <x:v>供发布值班查看候选对象</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>在空结果目录运行</x:v>
+        <x:v>按阶段解析YAML</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>构建程序</x:v>
+        <x:v>清单台账</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>output/tools/build_release_review.rb</x:v>
+        <x:v>output/results/manifest_ledger.csv</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>整理清单、样本和回退表</x:v>
+        <x:v>集中展示镜像、partition和基础字段</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>由执行入口调用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>与升级合同逐项比较</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>四阶段清单</x:v>
+        <x:v>历史观测整理表</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>output/results/rendered_base.yaml、rendered_canary.yaml、rendered_promote.yaml、rendered_rollback.yaml</x:v>
+        <x:v>output/results/ordinal_observation_review.csv</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>供发布值班查看候选对象</x:v>
+        <x:v>保留历史观测并标记就绪状态</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>按阶段解析YAML</x:v>
+        <x:v>按phase与ordinal连接输入</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>阶段字段表</x:v>
+        <x:v>阶段排期</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>output/results/render_contract.csv</x:v>
+        <x:v>output/results/stage_decisions.csv</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>集中展示镜像、partition和基础字段</x:v>
+        <x:v>记录维护窗阶段安排</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>与阶段合同逐项比较</x:v>
+        <x:v>按合同序号集合复核</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>探针复核表</x:v>
+        <x:v>回退检查表</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>output/results/probe_review.csv</x:v>
+        <x:v>output/results/rollback_checklist.csv</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>保留输入样本并计算样本状态</x:v>
+        <x:v>交给现场人员准备回退</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>按phase与ordinal连接输入</x:v>
+        <x:v>与合同回退步骤比较</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="5" t="str">
-        <x:v>阶段结论表</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>output/results/stage_gate_review.csv</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>给出继续或暂缓结论</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>按合同序号集合复算</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="5" t="str">
-        <x:v>回退检查表</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>output/results/rollback_checklist.csv</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>交给现场人员准备回退</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>与合同回退步骤比较</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="5" t="str">
-        <x:v>复核摘要</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>output/results/review_summary.json</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>说明材料范围与未执行动作</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>解析JSON字段</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="5" t="str">
-        <x:v>结果检查</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>output/results/validation.json</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>汇总程序检查结果</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="str">
-        <x:v>解析JSON后复算</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="6" t="str">
+      <x:c r="A9" s="6" t="str">
         <x:v>操作说明</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="B9" s="6" t="str">
         <x:v>output/README.md和output/commands/rollback_runbook.txt</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
-        <x:v>说明使用方式和现场动作</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="str">
-        <x:v>与实际路径及结果边界核对</x:v>
+      <x:c r="C9" s="6" t="str">
+        <x:v>说明材料用途和现场动作</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>与实际路径及结论边界核对</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -477,24 +418,24 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="54" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="46" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>交付物或对象</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>字段路径</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>正确值</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
-        <x:v>来源与验证</x:v>
+      <x:c r="D1" s="8" t="str">
+        <x:v>来源与核对</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
@@ -614,41 +555,27 @@
         <x:v>promote阶段</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>review_status</x:v>
+        <x:v>schedule_decision</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>SAMPLE_HOLD</x:v>
+        <x:v>HOLD</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>探针样本与阶段合同</x:v>
+        <x:v>历史观测与升级合同</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="5" t="str">
-        <x:v>复核摘要</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>scope</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>PRE_RELEASE_REVIEW</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>工作范围</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="6" t="str">
-        <x:v>结果检查</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="str">
-        <x:v>result</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="str">
-        <x:v>全部程序检查项通过</x:v>
+      <x:c r="A11" s="6" t="str">
+        <x:v>回退检查表</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>execution_status</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>维护窗尚未开始</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -660,29 +587,29 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="110" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="86" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>交付物或对象</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>字段或集合</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>正确集合</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>判定方式</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>渲染阶段</x:v>
+        <x:v>候选阶段</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>phase</x:v>
@@ -710,7 +637,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>canary样本</x:v>
+        <x:v>canary观测</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>ordinal</x:v>
@@ -719,12 +646,12 @@
         <x:v>4、3</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>与阶段合同匹配</x:v>
+        <x:v>与升级合同匹配</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>promote样本</x:v>
+        <x:v>promote观测</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>ordinal</x:v>
@@ -733,12 +660,12 @@
         <x:v>2、1</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>与阶段合同匹配</x:v>
+        <x:v>与升级合同匹配</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>rollback样本</x:v>
+        <x:v>rollback观测</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>ordinal</x:v>
@@ -747,49 +674,35 @@
         <x:v>4、3、2、1</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>与阶段合同匹配</x:v>
+        <x:v>与升级合同匹配</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>阶段结论</x:v>
+        <x:v>阶段排期</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>review_status</x:v>
+        <x:v>schedule_decision</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>SAMPLE_CLEAR、SAMPLE_HOLD</x:v>
+        <x:v>PROCEED、HOLD、READY_IF_APPROVED</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>三阶段逐项核对</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="5" t="str">
+      <x:c r="A8" s="6" t="str">
         <x:v>回退步骤</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="str">
+      <x:c r="B8" s="6" t="str">
         <x:v>step</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
+      <x:c r="C8" s="6" t="str">
         <x:v>1、2、3、4、5</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
+      <x:c r="D8" s="6" t="str">
         <x:v>集合连续且无重复</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>复核摘要</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>未执行动作字段</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>api_server_contacted、apply_executed、pod_deleted、controller_state_observed、pvc_state_observed、rollback_executed</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>字段集合精确匹配</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -802,27 +715,27 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="62" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>交付物或对象</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>字段或位置</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>正确值</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>容差</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
-        <x:v>来源与验证</x:v>
+      <x:c r="E1" s="8" t="str">
+        <x:v>来源与核对</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
@@ -856,7 +769,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>阶段合同</x:v>
+        <x:v>升级合同</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -873,7 +786,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>阶段合同</x:v>
+        <x:v>升级合同</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -890,7 +803,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>阶段合同</x:v>
+        <x:v>升级合同</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -907,7 +820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>阶段合同</x:v>
+        <x:v>升级合同</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -989,7 +902,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>以Gi为单位且精确匹配</x:v>
+        <x:v>以Gi为单位精确匹配</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
         <x:v>清单合同</x:v>
@@ -997,7 +910,7 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>probe_review.csv</x:v>
+        <x:v>ordinal_observation_review.csv</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
         <x:v>数据行数</x:v>
@@ -1009,12 +922,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E12" s="5" t="str">
-        <x:v>ordinal_probes.csv</x:v>
+        <x:v>ordinal_observations.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>stage_gate_review.csv</x:v>
+        <x:v>stage_decisions.csv</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
         <x:v>数据行数</x:v>
@@ -1055,23 +968,23 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="74" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="92" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>对象</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>允许变化</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>不可变化</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>判定方式</x:v>
       </x:c>
     </x:row>
@@ -1091,7 +1004,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>渲染YAML</x:v>
+        <x:v>候选YAML</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>文档顺序和键序可以变化</x:v>
@@ -1118,30 +1031,16 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="5" t="str">
-        <x:v>JSON结果</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>键序、缩进和空白可以变化</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="str">
-        <x:v>scope、布尔字段、控制量与结果不能变化</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>解析JSON后比较</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+      <x:c r="A5" s="6" t="str">
         <x:v>操作说明</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str">
+      <x:c r="B5" s="6" t="str">
         <x:v>段落和措辞可以变化</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
-        <x:v>使用入口、材料边界与现场动作状态不能变化</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="C5" s="6" t="str">
+        <x:v>材料边界与现场动作状态不能变化</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
         <x:v>定位实际路径并核对语义</x:v>
       </x:c>
     </x:row>
